--- a/amazon_ecommdata_sample.xlsx
+++ b/amazon_ecommdata_sample.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\siddi\Desktop\Portfolio\Leave Mgmt System\Amazon_ecomm_dataprofilingandquality\sql flies\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A35B90EA-C712-4BFE-B458-7A713846EC75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CB323D28-7D15-4EE4-B830-1AE29C21F883}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{66F922CD-210F-472E-8922-F32EBDF64678}"/>
   </bookViews>
@@ -1535,10 +1535,10 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" t="s">
         <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
       </c>
       <c r="K1" t="s">
         <v>10</v>
